--- a/estandar-c/templates/4-1-reporte-optimizacion.xlsx
+++ b/estandar-c/templates/4-1-reporte-optimizacion.xlsx
@@ -14,7 +14,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja 2 · Comparativo objetivo v" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja 3 · Calendario del siguien" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Tabla 1'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Referencia de trabajo del F21'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Tu turno · preguntas guía'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Hoja 1 · Métricas por publicaci'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Hoja 2 · Comparativo objetivo v'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Hoja 3 · Calendario del siguien'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -31,17 +38,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Afacad"/>
+      <name val="Calibri"/>
       <color rgb="004B5563"/>
-      <sz val="10"/>
+      <sz val="10.5"/>
     </font>
     <font>
-      <name val="Afacad"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,8 +61,13 @@
         <fgColor rgb="0028467E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F6FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -62,16 +75,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3E4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3E4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D3E4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3E4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +477,7 @@
     <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Mi CompañIA</t>
@@ -455,7 +485,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Reporte de desempeño del contenido publicado de marketing digital, documentado Manual de Marketing Digital con IA · Producto del Elemento 4 · Optimizar · Excel</t>
+          <t>Reporte de desempeño del contenido publicado de mercadotecnia digital, documentado Manual de Mercadotecnia Digital con IA · Producto del Elemento 4 · Optimizar · Excel</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -484,7 +514,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>MiPyME</t>
@@ -531,7 +561,7 @@
     <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -562,17 +592,17 @@
       <c r="C2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Resumen ejecutivo En 3-5 líneas: ¿qué pasó en el periodo? ¿Qué lograste vs qué esperabas?</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -588,17 +618,17 @@
       <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Comparativo contra objetivos de la estrategia ¿Qué objetivos habías definido? ¿Los cumpliste, los superaste o quedaste por debajo? Tabla de objetivo vs resultado real.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -614,17 +644,17 @@
       <c r="C6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Capturas de pantalla o evidencias Adjunta o describe las capturas de las herramientas de analítica que respaldan los datos del reporte.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -640,17 +670,17 @@
       <c r="C8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Pruebas de optimización propuestas ¿Qué pruebas A/B o multivariables propones para el siguiente periodo? Por cada una: qué hipótesis validas y con qué métrica.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -666,17 +696,17 @@
       <c r="C10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Ajuste de segmentación y presupuesto ¿Modificas la audiencia a la que llegas? ¿Ajustas el presupuesto de publicidad pagada? ¿Por qué?</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -692,17 +722,17 @@
       <c r="C12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Calendario del siguiente periodo Elabora el calendario de publicación para el siguiente mes o periodo.</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -718,17 +748,17 @@
       <c r="C14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Evidencia de aprobación ¿Cómo documenta la persona responsable que aprobó el plan? Correo, firma, captura.</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -757,7 +787,7 @@
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -831,20 +861,20 @@
       <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2">
-        <f>%</f>
-        <v/>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3">
+        <f>%</f>
+        <v/>
+      </c>
+      <c r="K3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr"/>
@@ -863,20 +893,20 @@
       <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2">
-        <f>%</f>
-        <v/>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3">
+        <f>%</f>
+        <v/>
+      </c>
+      <c r="K5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr"/>
@@ -895,20 +925,20 @@
       <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2">
-        <f>%</f>
-        <v/>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="A7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3">
+        <f>%</f>
+        <v/>
+      </c>
+      <c r="K7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
@@ -927,20 +957,20 @@
       <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2">
-        <f>%</f>
-        <v/>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="A9" s="3" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3">
+        <f>%</f>
+        <v/>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr"/>
@@ -959,20 +989,20 @@
       <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2">
-        <f>%</f>
-        <v/>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3">
+        <f>%</f>
+        <v/>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -995,7 +1025,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Objetivo</t>
@@ -1033,14 +1063,14 @@
       <c r="E2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2">
-        <f>%</f>
-        <v/>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3">
+        <f>%</f>
+        <v/>
+      </c>
+      <c r="E3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr"/>
@@ -1053,14 +1083,14 @@
       <c r="E4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2">
-        <f>%</f>
-        <v/>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3">
+        <f>%</f>
+        <v/>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr"/>
@@ -1096,7 +1126,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Semana</t>
@@ -1153,18 +1183,18 @@
       <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Semana 2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1181,18 +1211,18 @@
       <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Semana 4</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1209,18 +1239,18 @@
       <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Semana 6</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">

--- a/estandar-c/templates/4-1-reporte-optimizacion.xlsx
+++ b/estandar-c/templates/4-1-reporte-optimizacion.xlsx
@@ -7,16 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referencia de trabajo del F21" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guía" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos del documento" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tu turno · preguntas guía" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja 1 · Métricas por publicaci" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja 2 · Comparativo objetivo v" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja 3 · Calendario del siguien" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Tabla 1'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Referencia de trabajo del F21'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Datos del documento'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Tu turno · preguntas guía'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Hoja 1 · Métricas por publicaci'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Hoja 2 · Comparativo objetivo v'!$1:$1</definedName>
@@ -29,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +40,24 @@
       <name val="Calibri"/>
       <color rgb="004B5563"/>
       <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00529ED7"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0028467E"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0028467E"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -93,9 +110,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -469,28 +498,149 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mi CompañIA</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Reporte de desempeño del contenido publicado de mercadotecnia digital, documentado Manual de Mercadotecnia Digital con IA · Producto del Elemento 4 · Optimizar · Excel</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Producto 4.1 Hoja editable · Excel Mi CompañIA · FUNDES</t>
+          <t>PLANTILLA DE TRABAJO · ESTÁNDAR C</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Reporte de desempeño del contenido publicado de mercadotecnia digital, documentado</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sobre este template. Producto integrador que combina el reporte de desempeño de la campaña concluida con el plan de optimización para el siguiente periodo. Incluye métricas por publicación y por plataforma, comparativo contra objetivos, análisis de mejor y peor desempeño, recomendaciones de ajuste y el calendario del siguiente periodo. Debe contar con la aprobación de la persona responsable de mercadotecnia en la MiPyME. Excel es el formato natural para esta clase de producto: te permite añadir filas conforme registres más publicaciones, ordenar por métricas y generar gráficas. Llénalo con datos de TU MiPyME real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de trabajo del F21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>•  (a) Está elaborado a partir de una campaña de mercadotecnia digital concluida</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>•  (b) Tiene el resumen ejecutivo con los principales resultados alcanzados en el periodo analizado y su relación con los objetivos de la estrategia</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>•  (c) Incluye las métricas de rendimiento por publicación, por tipo de contenido y por plataforma digital, así como el comparativo respecto a la línea base de la MiPyME/indicadores de referencia de mercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>•  (d) Especifica el comparativo de resultados contra los objetivos medibles establecidos en la estrategia aprobada</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>•  (e) Contiene el análisis de mayor y menor rendimiento de los contenidos por tipo, formato, horario y plataforma digital, con la identificación de patrones de comportamiento y metas establecidas</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>•  (f) Incluye las capturas de pantalla/evidencias de los datos reportados por las herramientas de medición y seguimiento de las plataformas digitales</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>•  (g) Especifica la fecha del periodo de análisis, la fuente de los datos presentados y la frecuencia de medición</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>•  (h) Contiene las recomendaciones de continuidad/ajuste a los tipos de contenido/formatos/frecuencia de publicación por plataforma digital, con base en el análisis de resultados</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>•  (i) Indica la(s) propuesta(s) de pruebas de optimización a realizar, considerando la hipótesis a validar y la métrica de éxito</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>•  (j) Incluye la recomendación de continuidad/ajuste a horarios de publicación con base en los datos de rendimiento por plataforma digital y por tipo de contenido</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>•  (k) Contiene la recomendación de continuidad/modificación a la segmentación de audiencia y al presupuesto de promoción de acuerdo con los resultados obtenidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>•  (l) Incluye la propuesta de continuidad/ajuste a los prompts e instrucciones de generación de contenido con IA, considerando de los resultados de la campaña que concluyó</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>•  (m) Tiene el calendario de publicación de contenidos para el siguiente periodo</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>•  (n) Especifica los nuevos objetivos y métricas de seguimiento para el siguiente periodo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>•  (o) Contiene la evidencia de aprobación del plan de optimización por parte de la(s) persona(s) responsable(s) del mercadotecnia digital en la MiPyME</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="72" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Caso pedagógico Cafetería La Cuesta (ilustrativo): Campaña: septiembre 2025, 4 semanas. Resultados: Instagram +187 seguidores (meta: +200, -6.5%); Engagement rate promedio 4.2% (referencia mercado cafeterías: 2.8%); Alcance total: 8,420 personas. Mejor contenido: video Reel del origen del café (487 likes, 23 comentarios, 156 guardados). Peor contenido: imagen de menú con texto (12 likes, 0 comentarios). Patrón: el contenido educativo sobre café de especialidad tiene 3x más engagement que el contenido promocional directo. Plan de optimización: reducir posts de menú en un 50%, aumentar contenido educativo/origen del café, probar Reels de 30s (vs 15s actuales), publicar jueves 7pm en vez de viernes 6pm.</t>
         </is>
       </c>
     </row>
@@ -515,32 +665,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>MiPyME</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr"/>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr"/>
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr"/>
+      <c r="D1" s="5" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Consultor</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Responsable MiPyME</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -562,203 +712,203 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Pregunta guía</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Tu respuesta (llena con datos de TU MiPyME)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Periodo analizado y fuente de datos ¿Cuándo fue la campaña que estás analizando? ¿Qué fuentes usaste para obtener los datos (Meta Insights, Google Analytics, Hootsuite)? ¿Con qué frecuencia los mediste?</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Resumen ejecutivo En 3-5 líneas: ¿qué pasó en el periodo? ¿Qué lograste vs qué esperabas?</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Métricas por publicación, tipo de contenido y plataforma Tabla completa: por cada publicación (o por tipo de contenido agrupado), muestra alcance, impresiones, interacciones, tasa de interacción y otros KPIs relevantes.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Comparativo contra objetivos de la estrategia ¿Qué objetivos habías definido? ¿Los cumpliste, los superaste o quedaste por debajo? Tabla de objetivo vs resultado real.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Análisis de mejor y peor desempeño ¿Qué publicaciones o tipos de contenido funcionaron mejor? ¿Cuáles funcionaron peor? ¿Qué patrones de horario, formato o tema explican los resultados?</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Capturas de pantalla o evidencias Adjunta o describe las capturas de las herramientas de analítica que respaldan los datos del reporte.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Recomendaciones de ajuste (tipos, formatos, frecuencia) Con base en los resultados: ¿qué tipos de contenido vas a continuar? ¿Cuáles vas a eliminar o reducir? ¿Cambias la frecuencia?</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
+      <c r="C8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Pruebas de optimización propuestas ¿Qué pruebas A/B o multivariables propones para el siguiente periodo? Por cada una: qué hipótesis validas y con qué métrica.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Ajuste de horarios ¿Cambias los horarios de publicación? ¿Por qué? ¿Qué datos respaldan el cambio?</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
+      <c r="C10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Ajuste de segmentación y presupuesto ¿Modificas la audiencia a la que llegas? ¿Ajustas el presupuesto de publicidad pagada? ¿Por qué?</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Ajuste de prompts de IA ¿Qué cambios harás en los prompts que usas para generar contenido? ¿Qué aprendiste sobre qué tipos de prompts funcionan mejor para esta MiPyME?</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
+      <c r="C12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Calendario del siguiente periodo Elabora el calendario de publicación para el siguiente mes o periodo.</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
+      <c r="C13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Nuevos objetivos ¿Qué objetivos y métricas defines para el siguiente periodo, basándote en lo aprendido?</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
+      <c r="C14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Evidencia de aprobación ¿Cómo documenta la persona responsable que aprobó el plan? Correo, firma, captura.</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -783,226 +933,226 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Plataforma</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Tipo de contenido</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Alcance</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Impresiones</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Me gusta</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Comentarios</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Compartidos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Guardados</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Tasa de interacción %</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2">
-        <f>%</f>
+      <c r="A2" s="6" t="inlineStr"/>
+      <c r="B2" s="6" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr"/>
+      <c r="D2" s="6" t="inlineStr"/>
+      <c r="E2" s="6" t="inlineStr"/>
+      <c r="F2" s="6" t="inlineStr"/>
+      <c r="G2" s="6" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr"/>
+      <c r="I2" s="6" t="inlineStr"/>
+      <c r="J2" s="6">
+        <f>IFERROR(ROUND((F2+G2+H2+I2)/D2*100,2),"")</f>
         <v/>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="K2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3">
-        <f>%</f>
+      <c r="A3" s="7" t="inlineStr"/>
+      <c r="B3" s="7" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr"/>
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="inlineStr"/>
+      <c r="F3" s="7" t="inlineStr"/>
+      <c r="G3" s="7" t="inlineStr"/>
+      <c r="H3" s="7" t="inlineStr"/>
+      <c r="I3" s="7" t="inlineStr"/>
+      <c r="J3" s="7">
+        <f>IFERROR(ROUND((F3+G3+H3+I3)/D3*100,2),"")</f>
         <v/>
       </c>
-      <c r="K3" s="3" t="inlineStr"/>
+      <c r="K3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2">
-        <f>%</f>
+      <c r="A4" s="6" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6">
+        <f>IFERROR(ROUND((F4+G4+H4+I4)/D4*100,2),"")</f>
         <v/>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="K4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3">
-        <f>%</f>
+      <c r="A5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7">
+        <f>IFERROR(ROUND((F5+G5+H5+I5)/D5*100,2),"")</f>
         <v/>
       </c>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="K5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2">
-        <f>%</f>
+      <c r="A6" s="6" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6">
+        <f>IFERROR(ROUND((F6+G6+H6+I6)/D6*100,2),"")</f>
         <v/>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3">
-        <f>%</f>
+      <c r="A7" s="7" t="inlineStr"/>
+      <c r="B7" s="7" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7">
+        <f>IFERROR(ROUND((F7+G7+H7+I7)/D7*100,2),"")</f>
         <v/>
       </c>
-      <c r="K7" s="3" t="inlineStr"/>
+      <c r="K7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2">
-        <f>%</f>
+      <c r="A8" s="6" t="inlineStr"/>
+      <c r="B8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6">
+        <f>IFERROR(ROUND((F8+G8+H8+I8)/D8*100,2),"")</f>
         <v/>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3">
-        <f>%</f>
+      <c r="A9" s="7" t="inlineStr"/>
+      <c r="B9" s="7" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="7">
+        <f>IFERROR(ROUND((F9+G9+H9+I9)/D9*100,2),"")</f>
         <v/>
       </c>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2">
-        <f>%</f>
+      <c r="A10" s="6" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr"/>
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="6">
+        <f>IFERROR(ROUND((F10+G10+H10+I10)/D10*100,2),"")</f>
         <v/>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="K10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr"/>
-      <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3">
-        <f>%</f>
+      <c r="A11" s="7" t="inlineStr"/>
+      <c r="B11" s="7" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr"/>
+      <c r="J11" s="7">
+        <f>IFERROR(ROUND((F11+G11+H11+I11)/D11*100,2),"")</f>
         <v/>
       </c>
-      <c r="K11" s="3" t="inlineStr"/>
+      <c r="K11" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1021,86 +1171,86 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Meta definida</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Resultado real</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Variación %</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Cumplido (S/N)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2">
-        <f>%</f>
+      <c r="A2" s="6" t="inlineStr"/>
+      <c r="B2" s="6" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr"/>
+      <c r="D2" s="6">
+        <f>IFERROR(ROUND((C2-B2)/B2*100,2),"")</f>
         <v/>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3">
-        <f>%</f>
+      <c r="A3" s="7" t="inlineStr"/>
+      <c r="B3" s="7" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr"/>
+      <c r="D3" s="7">
+        <f>IFERROR(ROUND((C3-B3)/B3*100,2),"")</f>
         <v/>
       </c>
-      <c r="E3" s="3" t="inlineStr"/>
+      <c r="E3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2">
-        <f>%</f>
+      <c r="A4" s="6" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6">
+        <f>IFERROR(ROUND((C4-B4)/B4*100,2),"")</f>
         <v/>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3">
-        <f>%</f>
+      <c r="A5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7">
+        <f>IFERROR(ROUND((C5-B5)/B5*100,2),"")</f>
         <v/>
       </c>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2">
-        <f>%</f>
+      <c r="A6" s="6" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6">
+        <f>IFERROR(ROUND((C6-B6)/B6*100,2),"")</f>
         <v/>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1127,144 +1277,144 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Semana</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Domingo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Semana 1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="B2" s="6" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr"/>
+      <c r="D2" s="6" t="inlineStr"/>
+      <c r="E2" s="6" t="inlineStr"/>
+      <c r="F2" s="6" t="inlineStr"/>
+      <c r="G2" s="6" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Semana 2</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="B3" s="7" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr"/>
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="inlineStr"/>
+      <c r="F3" s="7" t="inlineStr"/>
+      <c r="G3" s="7" t="inlineStr"/>
+      <c r="H3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Semana 3</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Semana 4</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Semana 5</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Semana 6</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="B7" s="7" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Semana 7</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="B8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
